--- a/TestData/Registration_data.xlsx
+++ b/TestData/Registration_data.xlsx
@@ -1,97 +1,137 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
-  <workbookPr defaultThemeVersion="124226"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Swetha\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Software Testing\Interview Prep\Projects\Scan4Discount\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{141BE4BE-74A3-4ADE-8BD5-3027932E1748}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB7B3FF1-1420-4017-9CBE-45400CDDF5C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{6A7F12E6-8056-4803-8CED-87410553B0AE}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="2"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
-  <si>
-    <t>ShopName</t>
-  </si>
-  <si>
-    <t>OwnerName</t>
-  </si>
-  <si>
-    <t>EmailAddress</t>
-  </si>
-  <si>
-    <t>PhoneNumber</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="31">
+  <si>
+    <t>Case Type</t>
+  </si>
+  <si>
+    <t>Full Name</t>
+  </si>
+  <si>
+    <t>Phone Number</t>
+  </si>
+  <si>
+    <t>Email</t>
+  </si>
+  <si>
+    <t>Business Name</t>
   </si>
   <si>
     <t>City</t>
   </si>
   <si>
-    <t>Message</t>
-  </si>
-  <si>
-    <t>Tech Haven</t>
-  </si>
-  <si>
-    <t>Book Worms</t>
-  </si>
-  <si>
-    <t>Gourmet Bites</t>
-  </si>
-  <si>
-    <t>Alice Smith</t>
-  </si>
-  <si>
-    <t>Bob Jones</t>
-  </si>
-  <si>
-    <t>Charlie Brown</t>
-  </si>
-  <si>
-    <t>alice@techhaven.com</t>
-  </si>
-  <si>
-    <t>bob@bookworms.com</t>
-  </si>
-  <si>
-    <t>charlie@gourmet.com</t>
-  </si>
-  <si>
-    <t>1234567890</t>
-  </si>
-  <si>
-    <t>9876543210</t>
-  </si>
-  <si>
-    <t>5551234567</t>
+    <t>State</t>
+  </si>
+  <si>
+    <t>Pincode</t>
+  </si>
+  <si>
+    <t>Full Address</t>
+  </si>
+  <si>
+    <t>Positive</t>
+  </si>
+  <si>
+    <t>John Doe</t>
+  </si>
+  <si>
+    <t>john@test.com</t>
+  </si>
+  <si>
+    <t>My Shop</t>
   </si>
   <si>
     <t>Hyderabad</t>
   </si>
   <si>
-    <t>Secunderabad</t>
-  </si>
-  <si>
-    <t>Bangalore</t>
-  </si>
-  <si>
-    <t>Interested in features</t>
-  </si>
-  <si>
-    <t>Can you help me setup?</t>
-  </si>
-  <si>
-    <t>Need demo</t>
+    <t>Telangana</t>
+  </si>
+  <si>
+    <t>123 Main St</t>
+  </si>
+  <si>
+    <t>Negative - Empty Required</t>
+  </si>
+  <si>
+    <t>Negative - Invalid Phone</t>
+  </si>
+  <si>
+    <t>Negative - Invalid Email</t>
+  </si>
+  <si>
+    <t>invalid-email</t>
+  </si>
+  <si>
+    <t>Edge - Max Length Name</t>
+  </si>
+  <si>
+    <t>AAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAAA</t>
+  </si>
+  <si>
+    <t>j@test.com</t>
+  </si>
+  <si>
+    <t>Shop</t>
+  </si>
+  <si>
+    <t>Address</t>
+  </si>
+  <si>
+    <t>Edge - Pincode Min/Max</t>
+  </si>
+  <si>
+    <t>John</t>
+  </si>
+  <si>
+    <t>Negative - Special Characters in City</t>
+  </si>
+  <si>
+    <t>!@#$%</t>
+  </si>
+  <si>
+    <t>Optional - No GST</t>
+  </si>
+  <si>
+    <t>Status</t>
   </si>
 </sst>
 </file>
@@ -102,7 +142,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -134,7 +174,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -144,17 +184,30 @@
     </border>
     <border>
       <left style="thin">
-        <color auto="1"/>
+        <color indexed="64"/>
       </left>
       <right style="thin">
-        <color auto="1"/>
+        <color indexed="64"/>
       </right>
       <top style="thin">
-        <color auto="1"/>
+        <color indexed="64"/>
       </top>
       <bottom style="thin">
-        <color auto="1"/>
+        <color indexed="64"/>
       </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FFDDDDDD"/>
+      </left>
+      <right style="medium">
+        <color rgb="FFDDDDDD"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFDDDDDD"/>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
   </borders>
@@ -163,18 +216,18 @@
   </cellStyleXfs>
   <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -187,9 +240,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -197,44 +250,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="0E2841"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="E8E8E8"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="156082"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="E97132"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="196B24"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="0F9ED5"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="A02B93"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="4EA72E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="467886"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="800080"/>
+        <a:srgbClr val="96607D"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线 Light"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -262,14 +315,31 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hans" typeface="等线"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -297,9 +367,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -308,261 +395,449 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="35000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="37000"/>
-                <a:satMod val="300000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="15000"/>
-                <a:satMod val="350000"/>
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:shade val="51000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="80000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:shade val="93000"/>
-                <a:satMod val="130000"/>
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="94000"/>
-                <a:satMod val="135000"/>
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="0"/>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
+            <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-        </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
+                <a:alpha val="63000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="40000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="40000">
+            <a:gs pos="50000">
               <a:schemeClr val="phClr">
-                <a:tint val="45000"/>
-                <a:shade val="99000"/>
-                <a:satMod val="350000"/>
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="20000"/>
-                <a:satMod val="255000"/>
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
-          </a:path>
-        </a:gradFill>
-        <a:gradFill rotWithShape="1">
-          <a:gsLst>
-            <a:gs pos="0">
-              <a:schemeClr val="phClr">
-                <a:tint val="80000"/>
-                <a:satMod val="300000"/>
-              </a:schemeClr>
-            </a:gs>
-            <a:gs pos="100000">
-              <a:schemeClr val="phClr">
-                <a:shade val="30000"/>
-                <a:satMod val="200000"/>
-              </a:schemeClr>
-            </a:gs>
-          </a:gsLst>
-          <a:path path="circle">
-            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
-          </a:path>
+          <a:lin ang="5400000" scaled="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
+  <a:objectDefaults>
+    <a:lnDef>
+      <a:spPr/>
+      <a:bodyPr/>
+      <a:lstStyle/>
+      <a:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </a:style>
+    </a:lnDef>
+  </a:objectDefaults>
   <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+    </a:ext>
+  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{229936C8-A704-443E-B5EE-EE238EF777D4}">
+  <dimension ref="A1:J9"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.21875" customWidth="1"/>
-    <col min="2" max="2" width="14.88671875" customWidth="1"/>
-    <col min="3" max="3" width="23.5546875" customWidth="1"/>
-    <col min="4" max="4" width="19.88671875" customWidth="1"/>
-    <col min="5" max="5" width="17.33203125" customWidth="1"/>
-    <col min="6" max="6" width="26" customWidth="1"/>
+    <col min="1" max="2" width="17" customWidth="1"/>
+    <col min="3" max="3" width="19.109375" customWidth="1"/>
+    <col min="4" max="5" width="22.5546875" customWidth="1"/>
+    <col min="6" max="6" width="20.6640625" customWidth="1"/>
+    <col min="7" max="7" width="15.109375" customWidth="1"/>
+    <col min="8" max="8" width="13.44140625" customWidth="1"/>
+    <col min="9" max="9" width="17" customWidth="1"/>
+    <col min="10" max="10" width="16.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>30</v>
+      </c>
     </row>
-    <row r="2" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
+    <row r="2" spans="1:10" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="2">
+        <v>9876543210</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H2" s="2">
+        <v>500001</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J2" s="2"/>
+    </row>
+    <row r="3" spans="1:10" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2">
+        <v>9876543210</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H3" s="2">
+        <v>500001</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J3" s="2"/>
+    </row>
+    <row r="4" spans="1:10" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="2">
+        <v>123</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H4" s="2">
+        <v>500001</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J4" s="2"/>
+    </row>
+    <row r="5" spans="1:10" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="2">
+        <v>9876543210</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H5" s="2">
+        <v>500001</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J5" s="2"/>
+    </row>
+    <row r="6" spans="1:10" ht="156" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" s="2">
+        <v>9876543210</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" s="1" t="s">
+      <c r="H6" s="2">
+        <v>500001</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J6" s="2"/>
+    </row>
+    <row r="7" spans="1:10" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" s="2">
+        <v>9876543210</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="H7" s="2">
+        <v>0</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J7" s="2"/>
+    </row>
+    <row r="8" spans="1:10" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C8" s="2">
+        <v>9876543210</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H8" s="2">
+        <v>500001</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="J8" s="2"/>
+    </row>
+    <row r="9" spans="1:10" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="2">
+        <v>9876543210</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="F9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="H9" s="2">
+        <v>500001</v>
+      </c>
+      <c r="I9" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="E2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>23</v>
-      </c>
+      <c r="J9" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
